--- a/feedback_forms/019_precision_tools_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/019_precision_tools_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{1:_'high-temperature_oven'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{1: 'High-temperature oven'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{2:_'microplate'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{2: 'Microplate'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{3:_'sample_holder'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{3: 'Sample holder'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{4:_'pipettes'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{4: 'Pipettes'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{5:_'pipette_tips'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{5: 'Pipette tips'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{6:_'heating_block'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{6: 'Heating block'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{7:_'cooled_surface'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{7: 'Cooled surface'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{8:_'heating_elements'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{8: 'Heating elements'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{9:_'precision_balance'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{9: 'Precision balance'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{10:_'balance_scale'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{10: 'Balance scale'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{11:_'other_precision_tool'}</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{11: 'Other precision tool'}</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{1:_'yes'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{1: 'Yes'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{2:_'no'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{2: 'No'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{3:_'not_sure'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{3: 'Not sure'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{1:_'very_satisfied'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{1: 'Very satisfied'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{2:_'somewhat_satisfied'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{2: 'Somewhat satisfied'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{3:_'neutral'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{3: 'Neutral'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{4:_'somewhat_dissatisfied'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{4: 'Somewhat dissatisfied'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{5:_'very_dissatisfied'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{5: 'Very dissatisfied'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
